--- a/UtilitySymbols_Mapping.xlsx
+++ b/UtilitySymbols_Mapping.xlsx
@@ -61,6 +61,15 @@
     <x:t>Water Fitting</x:t>
   </x:si>
   <x:si>
+    <x:t>WAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEAAIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air Release Valve</x:t>
+  </x:si>
+  <x:si>
     <x:t>WM</x:t>
   </x:si>
   <x:si>
@@ -79,6 +88,24 @@
     <x:t>Water Meter</x:t>
   </x:si>
   <x:si>
+    <x:t>WBFP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEAWBFP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Water Back Flow Preventer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WBO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEAWBO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Water Blow Off</x:t>
+  </x:si>
+  <x:si>
     <x:t>HYD</x:t>
   </x:si>
   <x:si>
@@ -196,6 +223,24 @@
     <x:t>Catch Basin / Inlet</x:t>
   </x:si>
   <x:si>
+    <x:t>DI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Drop Inlet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JEAHW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Headwall</x:t>
+  </x:si>
+  <x:si>
     <x:t>E</x:t>
   </x:si>
   <x:si>
@@ -250,6 +295,15 @@
     <x:t>Electric Meter</x:t>
   </x:si>
   <x:si>
+    <x:t>WPP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E-POLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wood Power Pole</x:t>
+  </x:si>
+  <x:si>
     <x:t>G</x:t>
   </x:si>
   <x:si>
@@ -383,6 +437,33 @@
   </x:si>
   <x:si>
     <x:t>Chilled Water Vault</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPOLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Electric Utility Pole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBOX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E-BOX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Electric Utility Box</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utility Pole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utility Box</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1786,6 +1867,316 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId49" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 45"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId50" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 46"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId51" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 47"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId52" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 48"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId53" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 49"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId54" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 50"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId55" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 51"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId56" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 52"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId57" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="285750" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285750" cy="285750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId58" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2091,7 +2482,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D44"/>
+  <x:dimension ref="A1:D54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="15.710625" style="0" customWidth="1"/>
@@ -2195,37 +2586,37 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4" ht="35" customHeight="1">
       <x:c r="A10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4" ht="35" customHeight="1">
       <x:c r="A11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4" ht="35" customHeight="1">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>33</x:v>
@@ -2250,48 +2641,48 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4" ht="35" customHeight="1">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4" ht="35" customHeight="1">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4" ht="35" customHeight="1">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4" ht="35" customHeight="1">
       <x:c r="A18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>49</x:v>
@@ -2338,76 +2729,76 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4" ht="35" customHeight="1">
       <x:c r="A23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4" ht="35" customHeight="1">
       <x:c r="A24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4" ht="35" customHeight="1">
       <x:c r="A25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4" ht="35" customHeight="1">
       <x:c r="A26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4" ht="35" customHeight="1">
       <x:c r="A27" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4" ht="35" customHeight="1">
       <x:c r="A28" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
+      <x:c r="C28" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4" ht="35" customHeight="1">
@@ -2415,175 +2806,285 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4" ht="35" customHeight="1">
       <x:c r="A30" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4" ht="35" customHeight="1">
       <x:c r="A31" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4" ht="35" customHeight="1">
       <x:c r="A32" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4" ht="35" customHeight="1">
       <x:c r="A33" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4" ht="35" customHeight="1">
       <x:c r="A34" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4" ht="35" customHeight="1">
       <x:c r="A35" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4" ht="35" customHeight="1">
       <x:c r="A36" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4" ht="35" customHeight="1">
       <x:c r="A37" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4" ht="35" customHeight="1">
       <x:c r="A38" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4" ht="35" customHeight="1">
       <x:c r="A39" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4" ht="35" customHeight="1">
       <x:c r="A40" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4" ht="35" customHeight="1">
       <x:c r="A41" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4" ht="35" customHeight="1">
       <x:c r="A42" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4" ht="35" customHeight="1">
       <x:c r="A43" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4" ht="35" customHeight="1">
       <x:c r="A44" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A45" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A46" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A47" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A48" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A49" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A50" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A51" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A52" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A53" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4" ht="35" customHeight="1">
+      <x:c r="A54" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
